--- a/src/clients/8537932805-001/2026.Q2/sao kê.xlsx
+++ b/src/clients/8537932805-001/2026.Q2/sao kê.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data\8537932805-001\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1BDD42FC-07AF-454D-9F22-3D451BCD629D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B1A148C-1932-4E0A-8D7D-046A02A68B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7579B397-6F5F-4CDE-A17E-6D83BD0F77F3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{037FB73D-F50D-47CC-84E4-FDBF8C45773C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,48 +25,78 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
-  <si>
-    <t>Ngày</t>
-  </si>
-  <si>
-    <t>Giờ</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+  <si>
+    <t>STT</t>
+  </si>
+  <si>
+    <t>Thời gian</t>
+  </si>
+  <si>
+    <t>Nội dung giao dịch (Tóm tắt)</t>
   </si>
   <si>
     <t>Số tiền (VND)</t>
   </si>
   <si>
-    <t>Số dư sau giao dịch (VND)</t>
-  </si>
-  <si>
-    <t>Nội dung / Mô tả giao dịch</t>
-  </si>
-  <si>
-    <t>Mã tham chiếu (Ref)</t>
-  </si>
-  <si>
-    <t>Thu từ TikTok Shop</t>
-  </si>
-  <si>
-    <t>SP#020097042206261310202619BD351795.5189.39594.131810</t>
-  </si>
-  <si>
-    <t>Chuyển tiền đến HỘ KINH DOANH HOANG THACH (Hoàn tiền)</t>
-  </si>
-  <si>
-    <t>MBBIZ.6071059326.048703</t>
-  </si>
-  <si>
-    <t>MBBIZ.6071059928.6177BFTVG271FHW8</t>
-  </si>
-  <si>
-    <t>MBBIZ.6071060447.050004</t>
-  </si>
-  <si>
-    <t>Rút tiền mặt tại quỹ</t>
-  </si>
-  <si>
-    <t>MBBIZ.6071062196.6177BFTVG271JUW9</t>
+    <t>Chuyển khoản từ 3BROTHERS (IBBIZ606...)</t>
+  </si>
+  <si>
+    <t>Rút tiền mặt (MBBIZ606...)</t>
+  </si>
+  <si>
+    <t>Doanh thu TikTok Shop</t>
+  </si>
+  <si>
+    <t>Đặt cọc/Hợp đồng (6098ASCB...)</t>
+  </si>
+  <si>
+    <t>Chuyển khoản từ Meishang VN (IBBIZ606...)</t>
+  </si>
+  <si>
+    <t>Nộp thuế nội bộ (INTERNAL_TAX_PAYMENT...)</t>
+  </si>
+  <si>
+    <t>Chuyển khoản từ CT TNHH MY PHAM LJ...</t>
+  </si>
+  <si>
+    <t>Chuyển khoản từ CT TNHH NOVO (IBBIZ606...)</t>
+  </si>
+  <si>
+    <t>Lãi tiền gửi (INTEREST PAYMENT)</t>
+  </si>
+  <si>
+    <t>Chuyển khoản từ Cty biocare...</t>
+  </si>
+  <si>
+    <t>Đặt cọc/Hợp đồng (OVERALL COC 50 asc...)</t>
+  </si>
+  <si>
+    <t>Thanh toán chuyển tiền qua IBPS (MBBIZ606...)</t>
+  </si>
+  <si>
+    <t>Chuyển khoản từ CRE THANH (6137ASC...)</t>
+  </si>
+  <si>
+    <t>Chuyển khoản từ HKD CAN THI (6140IBT...)</t>
+  </si>
+  <si>
+    <t>Thu phí quản lý tài khoản tổ chức</t>
+  </si>
+  <si>
+    <t>Doanh thu TikTok Shop (Nhận tiền)</t>
+  </si>
+  <si>
+    <t>Hoàn tiền từ HKD Hoàng Thạch (Thứ 1)</t>
+  </si>
+  <si>
+    <t>Hoàn tiền từ HKD Hoàng Thạch (Thứ 2)</t>
+  </si>
+  <si>
+    <t>Hoàn tiền từ HKD Hoàng Thạch (Thứ 3)</t>
+  </si>
+  <si>
+    <t>Rút tiền mặt nhập quỹ (MBBIZ.607...)</t>
   </si>
 </sst>
 </file>
@@ -104,8 +134,8 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -419,19 +449,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FA90C7C-59A6-4DEF-A5BB-6632F0C7FF4D}">
-  <dimension ref="A1:F6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD7090DB-F5FE-4972-A5DD-EC9DFB66CF95}">
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="61.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="55.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -444,111 +472,327 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>46113</v>
+      </c>
+      <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="D2" s="2">
+        <v>35000000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>46119</v>
+      </c>
+      <c r="C3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>46199</v>
-      </c>
-      <c r="B2" s="2">
-        <v>0.5541666666666667</v>
-      </c>
-      <c r="C2" s="3">
-        <v>89996756</v>
-      </c>
-      <c r="D2" s="3">
-        <v>176714267</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D3" s="2">
+        <v>-120000000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>46119</v>
+      </c>
+      <c r="C4" t="s">
         <v>6</v>
       </c>
-      <c r="F2" t="s">
+      <c r="D4" s="2">
+        <v>33656754</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>46120</v>
+      </c>
+      <c r="C5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
-        <v>46199</v>
-      </c>
-      <c r="B3" s="2">
-        <v>0.62013888888888891</v>
-      </c>
-      <c r="C3" s="3">
+      <c r="D5" s="2">
+        <v>16500000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>46129</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2">
+        <v>30250000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
+        <v>46129</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2">
+        <v>-23095366</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
+        <v>46133</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="2">
+        <v>13625000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
+        <v>46136</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="2">
+        <v>12535000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <v>46137</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="2">
+        <v>8672</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
+        <v>46139</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="2">
+        <v>27500000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1">
+        <v>46141</v>
+      </c>
+      <c r="C12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="2">
+        <v>-130000000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1">
+        <v>46141</v>
+      </c>
+      <c r="C13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="2">
+        <v>49496753</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1">
+        <v>46146</v>
+      </c>
+      <c r="C14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="2">
+        <v>16500000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1">
+        <v>46149</v>
+      </c>
+      <c r="C15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="2">
+        <v>-3240000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1">
+        <v>46159</v>
+      </c>
+      <c r="C16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="2">
+        <v>43600000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1">
+        <v>46162</v>
+      </c>
+      <c r="C17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="2">
+        <v>14980000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1">
+        <v>46167</v>
+      </c>
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="2">
+        <v>6330</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1">
+        <v>46167</v>
+      </c>
+      <c r="C19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="2">
+        <v>-22000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3">
+        <v>46199.554282407407</v>
+      </c>
+      <c r="C20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="2">
+        <v>98996756</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3">
+        <v>46199.620671296296</v>
+      </c>
+      <c r="C21" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="2">
         <v>-16500000</v>
       </c>
-      <c r="D3" s="3">
-        <v>160214267</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
-        <v>46199</v>
-      </c>
-      <c r="B4" s="2">
-        <v>0.62152777777777779</v>
-      </c>
-      <c r="C4" s="3">
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3">
+        <v>46199.621886574074</v>
+      </c>
+      <c r="C22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="2">
         <v>-14980000</v>
       </c>
-      <c r="D4" s="3">
-        <v>145234267</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
-        <v>46199</v>
-      </c>
-      <c r="B5" s="2">
-        <v>0.62291666666666667</v>
-      </c>
-      <c r="C5" s="3">
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3">
+        <v>46199.623171296298</v>
+      </c>
+      <c r="C23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="2">
         <v>-43600000</v>
       </c>
-      <c r="D5" s="3">
-        <v>101634267</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
-        <v>46199</v>
-      </c>
-      <c r="B6" s="2">
-        <v>0.62777777777777777</v>
-      </c>
-      <c r="C6" s="3">
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3">
+        <v>46199.627858796295</v>
+      </c>
+      <c r="C24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="2">
         <v>-100000000</v>
-      </c>
-      <c r="D6" s="3">
-        <v>1634267</v>
-      </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
